--- a/output_data/charts/crashSeverityByType-Madison.xlsx
+++ b/output_data/charts/crashSeverityByType-Madison.xlsx
@@ -31,12 +31,12 @@
     <t>Fixed Object</t>
   </si>
   <si>
+    <t>Head On</t>
+  </si>
+  <si>
     <t>Rear End</t>
   </si>
   <si>
-    <t>Head On</t>
-  </si>
-  <si>
     <t>Angle</t>
   </si>
   <si>
@@ -46,34 +46,34 @@
     <t>Animal</t>
   </si>
   <si>
+    <t>Parked Vehicle</t>
+  </si>
+  <si>
+    <t>Sideswipe - Passing</t>
+  </si>
+  <si>
+    <t>Sideswipe - Meeting</t>
+  </si>
+  <si>
+    <t>Right Turn</t>
+  </si>
+  <si>
     <t>Overturning</t>
   </si>
   <si>
+    <t>Pedalcycles</t>
+  </si>
+  <si>
+    <t>Other Object</t>
+  </si>
+  <si>
+    <t>Other Non-Collision</t>
+  </si>
+  <si>
+    <t>Left Turn</t>
+  </si>
+  <si>
     <t>Backing</t>
-  </si>
-  <si>
-    <t>Left Turn</t>
-  </si>
-  <si>
-    <t>Other Object</t>
-  </si>
-  <si>
-    <t>Other Non-Collision</t>
-  </si>
-  <si>
-    <t>Pedalcycles</t>
-  </si>
-  <si>
-    <t>Parked Vehicle</t>
-  </si>
-  <si>
-    <t>Right Turn</t>
-  </si>
-  <si>
-    <t>Sideswipe - Meeting</t>
-  </si>
-  <si>
-    <t>Sideswipe - Passing</t>
   </si>
   <si>
     <t>Unknown</t>
@@ -216,10 +216,10 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Head On</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Angle</c:v>
@@ -231,34 +231,34 @@
                   <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Overturning</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
+                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Passing</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -273,25 +273,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>38.23529411764706</c:v>
+                  <c:v>38.88888888888889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.64705882352941</c:v>
+                  <c:v>19.44444444444445</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.64705882352941</c:v>
+                  <c:v>16.66666666666666</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.70588235294118</c:v>
+                  <c:v>13.88888888888889</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.88235294117647</c:v>
+                  <c:v>5.555555555555555</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.941176470588235</c:v>
+                  <c:v>2.777777777777778</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.941176470588235</c:v>
+                  <c:v>2.777777777777778</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -358,10 +358,10 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Head On</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Angle</c:v>
@@ -373,34 +373,34 @@
                   <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Overturning</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
+                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Passing</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -415,52 +415,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>32.74336283185841</c:v>
+                  <c:v>34.14634146341464</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.69911504424779</c:v>
+                  <c:v>3.414634146341464</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.539823008849558</c:v>
+                  <c:v>15.60975609756098</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.69911504424779</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.309734513274337</c:v>
+                  <c:v>3.902439024390244</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.769911504424779</c:v>
+                  <c:v>1.951219512195122</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.654867256637168</c:v>
+                  <c:v>1.951219512195122</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8849557522123894</c:v>
+                  <c:v>4.390243902439024</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.424778761061947</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1.951219512195122</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.926829268292683</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.463414634146342</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.654867256637168</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.769911504424779</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.769911504424779</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.327433628318584</c:v>
+                  <c:v>1.951219512195122</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>5.365853658536586</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.752212389380531</c:v>
+                  <c:v>0.975609756097561</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -500,10 +500,10 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Head On</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Angle</c:v>
@@ -515,34 +515,34 @@
                   <c:v>Animal</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Overturning</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
+                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Passing</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -557,55 +557,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>27.65916522408155</c:v>
+                  <c:v>26.47754137115839</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.82996730140412</c:v>
+                  <c:v>1.792750197005516</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.750336603192922</c:v>
+                  <c:v>15.74074074074074</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.0019234468167</c:v>
+                  <c:v>10.77620173364854</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5577995768417003</c:v>
+                  <c:v>0.4334121355397951</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.847855356799386</c:v>
+                  <c:v>8.687943262411348</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.211771494518177</c:v>
+                  <c:v>3.230890464933018</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.366031929217157</c:v>
+                  <c:v>15.16942474389283</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.693017888055395</c:v>
+                  <c:v>0.5319148936170213</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.961915753029429</c:v>
+                  <c:v>1.556343577620173</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.500673206385843</c:v>
+                  <c:v>1.339637509850276</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1923446816695518</c:v>
+                  <c:v>0.2167060677698976</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.192921715714561</c:v>
+                  <c:v>1.950354609929078</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.538757453356415</c:v>
+                  <c:v>3.546099290780142</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.3269859588382382</c:v>
+                  <c:v>3.38849487785658</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>14.75283708405463</c:v>
+                  <c:v>3.605200945626478</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.615695326024235</c:v>
+                  <c:v>1.556343577620173</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>38.23529411764706</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="C2" s="2">
-        <v>32.74336283185841</v>
+        <v>34.14634146341464</v>
       </c>
       <c r="D2" s="2">
-        <v>27.65916522408155</v>
+        <v>26.47754137115839</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>17.64705882352941</v>
+        <v>19.44444444444445</v>
       </c>
       <c r="C3" s="2">
-        <v>17.69911504424779</v>
+        <v>3.414634146341464</v>
       </c>
       <c r="D3" s="2">
-        <v>15.82996730140412</v>
+        <v>1.792750197005516</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>17.64705882352941</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="C4" s="2">
-        <v>3.539823008849558</v>
+        <v>15.60975609756098</v>
       </c>
       <c r="D4" s="2">
-        <v>1.750336603192922</v>
+        <v>15.74074074074074</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>14.70588235294118</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="C5" s="2">
-        <v>17.69911504424779</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
-        <v>10.0019234468167</v>
+        <v>10.77620173364854</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>5.88235294117647</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="C6" s="2">
-        <v>5.309734513274337</v>
+        <v>3.902439024390244</v>
       </c>
       <c r="D6" s="2">
-        <v>0.5577995768417003</v>
+        <v>0.4334121355397951</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>2.941176470588235</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="C7" s="2">
-        <v>1.769911504424779</v>
+        <v>1.951219512195122</v>
       </c>
       <c r="D7" s="2">
-        <v>8.847855356799386</v>
+        <v>8.687943262411348</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1145,13 +1145,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>2.941176470588235</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="C8" s="2">
-        <v>2.654867256637168</v>
+        <v>1.951219512195122</v>
       </c>
       <c r="D8" s="2">
-        <v>1.211771494518177</v>
+        <v>3.230890464933018</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="2">
-        <v>0.8849557522123894</v>
+        <v>4.390243902439024</v>
       </c>
       <c r="D9" s="2">
-        <v>3.366031929217157</v>
+        <v>15.16942474389283</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="2">
-        <v>4.424778761061947</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>3.693017888055395</v>
+        <v>0.5319148936170213</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>1.951219512195122</v>
       </c>
       <c r="D11" s="2">
-        <v>1.961915753029429</v>
+        <v>1.556343577620173</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1204,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <v>2.654867256637168</v>
+        <v>2.926829268292683</v>
       </c>
       <c r="D12" s="2">
-        <v>3.500673206385843</v>
+        <v>1.339637509850276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <v>1.769911504424779</v>
+        <v>1.463414634146342</v>
       </c>
       <c r="D13" s="2">
-        <v>0.1923446816695518</v>
+        <v>0.2167060677698976</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>1.769911504424779</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>3.192921715714561</v>
+        <v>1.950354609929078</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>1.327433628318584</v>
+        <v>1.951219512195122</v>
       </c>
       <c r="D15" s="2">
-        <v>1.538757453356415</v>
+        <v>3.546099290780142</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>5.365853658536586</v>
       </c>
       <c r="D16" s="2">
-        <v>0.3269859588382382</v>
+        <v>3.38849487785658</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>5.752212389380531</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="D17" s="2">
-        <v>14.75283708405463</v>
+        <v>3.605200945626478</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>1.615695326024235</v>
+        <v>1.556343577620173</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Madison.xlsx
+++ b/output_data/charts/crashSeverityByType-Madison.xlsx
@@ -83,8 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -141,7 +142,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -173,7 +174,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Madison County</a:t>
+              <a:t>Crash Severity by Type of Crash, Madison County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
